--- a/13756_Cuenca_Huaura/_raw_reportes_xlsx/IDConfig_64884_completo.xlsx
+++ b/13756_Cuenca_Huaura/_raw_reportes_xlsx/IDConfig_64884_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R44755bb341ef414f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Re3baf100ea154368"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
       </x:c>
       <x:c s="" t="inlineStr">
         <x:is>
-          <x:t>Dpto: Lima / Prov: Oyon / Dist.: Pachangara</x:t>
+          <x:t>Dpto: Lima / Prov: Oyón / Dist.: Pachangara</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -250,6 +250,141 @@
         <x:is>
           <x:t>VALOR (m³/s)</x:t>
         </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6969</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9858</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7019</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6773</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8493</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7508</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8247</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1145</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/13756_Cuenca_Huaura/_raw_reportes_xlsx/IDConfig_64884_completo.xlsx
+++ b/13756_Cuenca_Huaura/_raw_reportes_xlsx/IDConfig_64884_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Re3baf100ea154368"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R049281043b104d5d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6355</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6618</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6197</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6489</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.7357</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.5673</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6249</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.5935</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3597</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6354</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6565</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.7040</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6670</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.5777</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1789</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.2416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1957</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.2160</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1652</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3546</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.5360</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4896</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4061</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3495</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4113</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4631</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4476</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4165</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4838</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.5674</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.2984</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4321</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4216</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3185</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4374</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3754</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.5935</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.5243</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.5359</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4319</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.2877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3705</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.2671</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3958</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.2727</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9908</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
